--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1262,6 +1262,134 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123689950</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57481</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bastuskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>767760</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7072680</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Roger Olofsson, Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>123619204</v>
       </c>
       <c r="B5" t="n">
-        <v>57125</v>
+        <v>57131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>123619198</v>
       </c>
       <c r="B6" t="n">
-        <v>56683</v>
+        <v>56689</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>123689950</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>123619204</v>
       </c>
       <c r="B5" t="n">
-        <v>57131</v>
+        <v>57134</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>123619198</v>
       </c>
       <c r="B6" t="n">
-        <v>56689</v>
+        <v>56692</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>123689950</v>
       </c>
       <c r="B7" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123619204</v>
+        <v>123619198</v>
       </c>
       <c r="B5" t="n">
-        <v>57134</v>
+        <v>56692</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102964</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1053,7 +1053,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1109,6 +1109,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stöttes</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123619198</v>
+        <v>123619204</v>
       </c>
       <c r="B6" t="n">
-        <v>56692</v>
+        <v>57135</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1156,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>102964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1177,7 +1182,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1233,11 +1238,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stöttes</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,7 +1267,7 @@
         <v>123689950</v>
       </c>
       <c r="B7" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123619198</v>
+        <v>123619204</v>
       </c>
       <c r="B5" t="n">
-        <v>56692</v>
+        <v>57135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>102964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1053,7 +1053,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1109,11 +1109,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Stöttes</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123619204</v>
+        <v>123619198</v>
       </c>
       <c r="B6" t="n">
-        <v>57135</v>
+        <v>56692</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102964</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1182,7 +1177,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1238,6 +1233,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stöttes</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123619204</v>
+        <v>123619198</v>
       </c>
       <c r="B5" t="n">
-        <v>57135</v>
+        <v>56692</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102964</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1053,7 +1053,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1109,6 +1109,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stöttes</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123619198</v>
+        <v>123619204</v>
       </c>
       <c r="B6" t="n">
-        <v>56692</v>
+        <v>57135</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1156,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>102964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1177,7 +1182,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1233,11 +1238,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stöttes</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124497448</v>
+        <v>124497451</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>57429</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,38 +1506,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100067</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767829</v>
+        <v>767666</v>
       </c>
       <c r="R9" t="n">
-        <v>7072722</v>
+        <v>7072608</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1698,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124497451</v>
+        <v>124497448</v>
       </c>
       <c r="B11" t="n">
-        <v>57429</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,52 +1724,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100067</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767666</v>
+        <v>767829</v>
       </c>
       <c r="R11" t="n">
-        <v>7072608</v>
+        <v>7072722</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124497451</v>
+        <v>124497448</v>
       </c>
       <c r="B9" t="n">
-        <v>57429</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,52 +1506,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100067</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767666</v>
+        <v>767829</v>
       </c>
       <c r="R9" t="n">
-        <v>7072608</v>
+        <v>7072722</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1610,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124497453</v>
+        <v>124497451</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>57429</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,34 +1612,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100067</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767709</v>
+        <v>767666</v>
       </c>
       <c r="R10" t="n">
-        <v>7072638</v>
+        <v>7072608</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124497448</v>
+        <v>124497453</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,25 +1724,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767829</v>
+        <v>767709</v>
       </c>
       <c r="R11" t="n">
-        <v>7072722</v>
+        <v>7072638</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124497448</v>
+        <v>124497451</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>57429</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,38 +1506,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100067</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767829</v>
+        <v>767666</v>
       </c>
       <c r="R9" t="n">
-        <v>7072722</v>
+        <v>7072608</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1596,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124497451</v>
+        <v>124497448</v>
       </c>
       <c r="B10" t="n">
-        <v>57429</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,52 +1622,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100067</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767666</v>
+        <v>767829</v>
       </c>
       <c r="R10" t="n">
-        <v>7072608</v>
+        <v>7072722</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124497451</v>
+        <v>124497453</v>
       </c>
       <c r="B9" t="n">
-        <v>57429</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,48 +1510,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100067</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767666</v>
+        <v>767709</v>
       </c>
       <c r="R9" t="n">
-        <v>7072608</v>
+        <v>7072638</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1610,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124497448</v>
+        <v>124497451</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>57429</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,38 +1608,52 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100067</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767829</v>
+        <v>767666</v>
       </c>
       <c r="R10" t="n">
-        <v>7072722</v>
+        <v>7072608</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124497453</v>
+        <v>124497448</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,25 +1724,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767709</v>
+        <v>767829</v>
       </c>
       <c r="R11" t="n">
-        <v>7072638</v>
+        <v>7072722</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124497453</v>
+        <v>124497451</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>57429</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,34 +1510,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100067</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767709</v>
+        <v>767666</v>
       </c>
       <c r="R9" t="n">
-        <v>7072638</v>
+        <v>7072608</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1596,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124497451</v>
+        <v>124497453</v>
       </c>
       <c r="B10" t="n">
-        <v>57429</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,48 +1626,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100067</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767666</v>
+        <v>767709</v>
       </c>
       <c r="R10" t="n">
-        <v>7072608</v>
+        <v>7072638</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124497451</v>
+        <v>124497453</v>
       </c>
       <c r="B9" t="n">
-        <v>57429</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,48 +1510,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100067</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767666</v>
+        <v>767709</v>
       </c>
       <c r="R9" t="n">
-        <v>7072608</v>
+        <v>7072638</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1610,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124497453</v>
+        <v>124497451</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>57429</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,34 +1612,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100067</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767709</v>
+        <v>767666</v>
       </c>
       <c r="R10" t="n">
-        <v>7072638</v>
+        <v>7072608</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124497453</v>
+        <v>124497451</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>57429</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,34 +1510,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100067</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767709</v>
+        <v>767666</v>
       </c>
       <c r="R9" t="n">
-        <v>7072638</v>
+        <v>7072608</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1596,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124497451</v>
+        <v>124497448</v>
       </c>
       <c r="B10" t="n">
-        <v>57429</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,52 +1622,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100067</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767666</v>
+        <v>767829</v>
       </c>
       <c r="R10" t="n">
-        <v>7072608</v>
+        <v>7072722</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124497448</v>
+        <v>124497453</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,25 +1724,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767829</v>
+        <v>767709</v>
       </c>
       <c r="R11" t="n">
-        <v>7072722</v>
+        <v>7072638</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124497451</v>
+        <v>124497453</v>
       </c>
       <c r="B9" t="n">
-        <v>57429</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,48 +1510,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100067</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767666</v>
+        <v>767709</v>
       </c>
       <c r="R9" t="n">
-        <v>7072608</v>
+        <v>7072638</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1712,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124497453</v>
+        <v>124497451</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>57429</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,34 +1714,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100067</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767709</v>
+        <v>767666</v>
       </c>
       <c r="R11" t="n">
-        <v>7072638</v>
+        <v>7072608</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124497448</v>
+        <v>124497451</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>57429</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,38 +1608,52 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100067</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767829</v>
+        <v>767666</v>
       </c>
       <c r="R10" t="n">
-        <v>7072722</v>
+        <v>7072608</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1698,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124497451</v>
+        <v>124497448</v>
       </c>
       <c r="B11" t="n">
-        <v>57429</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,52 +1724,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100067</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767666</v>
+        <v>767829</v>
       </c>
       <c r="R11" t="n">
-        <v>7072608</v>
+        <v>7072722</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124497453</v>
+        <v>124497448</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,25 +1506,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767709</v>
+        <v>767829</v>
       </c>
       <c r="R9" t="n">
-        <v>7072638</v>
+        <v>7072722</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124497451</v>
+        <v>124497453</v>
       </c>
       <c r="B10" t="n">
-        <v>57429</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,48 +1612,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100067</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767666</v>
+        <v>767709</v>
       </c>
       <c r="R10" t="n">
-        <v>7072608</v>
+        <v>7072638</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124497448</v>
+        <v>124497451</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>57429</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,38 +1710,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100067</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767829</v>
+        <v>767666</v>
       </c>
       <c r="R11" t="n">
-        <v>7072722</v>
+        <v>7072608</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124497448</v>
+        <v>124497453</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,25 +1506,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767829</v>
+        <v>767709</v>
       </c>
       <c r="R9" t="n">
-        <v>7072722</v>
+        <v>7072638</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124497453</v>
+        <v>124497451</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>57429</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,34 +1612,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100067</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767709</v>
+        <v>767666</v>
       </c>
       <c r="R10" t="n">
-        <v>7072638</v>
+        <v>7072608</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1698,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124497451</v>
+        <v>124497448</v>
       </c>
       <c r="B11" t="n">
-        <v>57429</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,52 +1724,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100067</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bastuskär, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767666</v>
+        <v>767829</v>
       </c>
       <c r="R11" t="n">
-        <v>7072608</v>
+        <v>7072722</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124497448</v>
+        <v>124497453</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,25 +1506,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767829</v>
+        <v>767709</v>
       </c>
       <c r="R9" t="n">
-        <v>7072722</v>
+        <v>7072638</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124497453</v>
+        <v>124497448</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,25 +1608,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767709</v>
+        <v>767829</v>
       </c>
       <c r="R10" t="n">
-        <v>7072638</v>
+        <v>7072722</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1812,6 +1812,118 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125424540</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bastuskäret, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>767559</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7072540</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1817,7 +1817,7 @@
         <v>125424540</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>91131</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1817,12 +1817,7 @@
         <v>125424540</v>
       </c>
       <c r="B12" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1817,7 +1817,7 @@
         <v>125424540</v>
       </c>
       <c r="B12" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1817,7 +1817,7 @@
         <v>125424540</v>
       </c>
       <c r="B12" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1817,7 +1817,7 @@
         <v>125424540</v>
       </c>
       <c r="B12" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1919,6 +1919,108 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127804548</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bastuskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>767780</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7072519</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1924,7 +1924,7 @@
         <v>127804548</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1924,7 +1924,7 @@
         <v>127804548</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2021,6 +2021,354 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128216810</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91757</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bastuskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>767829</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7072653</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt innan stormen</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt innan stormen</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Roger Olofsson, Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128216812</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57618</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bastuskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>767869</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7072656</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ganska blåsigt. Flög och svävade över oss vid skogsranden/havskanten. De var inte så brydda över vår närvaro verkade det som.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Roger Olofsson, Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128216301</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91346</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bastuskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>767862</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7072696</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -2026,7 +2026,7 @@
         <v>128216810</v>
       </c>
       <c r="B14" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>128216301</v>
       </c>
       <c r="B16" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -2026,7 +2026,7 @@
         <v>128216810</v>
       </c>
       <c r="B14" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>128216301</v>
       </c>
       <c r="B16" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1924,7 +1924,7 @@
         <v>127804548</v>
       </c>
       <c r="B13" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>128216810</v>
       </c>
       <c r="B14" t="n">
-        <v>91759</v>
+        <v>91767</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128216812</v>
       </c>
       <c r="B15" t="n">
-        <v>57618</v>
+        <v>57619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>128216301</v>
       </c>
       <c r="B16" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -1924,7 +1924,7 @@
         <v>127804548</v>
       </c>
       <c r="B13" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>128216810</v>
       </c>
       <c r="B14" t="n">
-        <v>91767</v>
+        <v>91859</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128216812</v>
       </c>
       <c r="B15" t="n">
-        <v>57619</v>
+        <v>57631</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>128216301</v>
       </c>
       <c r="B16" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -2026,7 +2026,7 @@
         <v>128216810</v>
       </c>
       <c r="B14" t="n">
-        <v>91859</v>
+        <v>91871</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128216812</v>
       </c>
       <c r="B15" t="n">
-        <v>57631</v>
+        <v>57635</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>128216301</v>
       </c>
       <c r="B16" t="n">
-        <v>91448</v>
+        <v>91460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -2026,7 +2026,7 @@
         <v>128216810</v>
       </c>
       <c r="B14" t="n">
-        <v>91871</v>
+        <v>91873</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Roger Olofsson, Jon Andersson</t>
+          <t>Jon Andersson, Roger Olofsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2262,7 +2262,7 @@
         <v>128216301</v>
       </c>
       <c r="B16" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -2128,7 +2128,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jon Andersson, Roger Olofsson</t>
+          <t>Roger Olofsson, Jon Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -2026,7 +2026,7 @@
         <v>128216810</v>
       </c>
       <c r="B14" t="n">
-        <v>91873</v>
+        <v>91874</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Roger Olofsson, Jon Andersson</t>
+          <t>Jon Andersson, Roger Olofsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2262,7 +2262,7 @@
         <v>128216301</v>
       </c>
       <c r="B16" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 11797-2025 artfynd.xlsx
+++ b/artfynd/A 11797-2025 artfynd.xlsx
@@ -2026,7 +2026,7 @@
         <v>128216810</v>
       </c>
       <c r="B14" t="n">
-        <v>91874</v>
+        <v>91901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jon Andersson, Roger Olofsson</t>
+          <t>Roger Olofsson, Jon Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2138,7 +2138,7 @@
         <v>128216812</v>
       </c>
       <c r="B15" t="n">
-        <v>57635</v>
+        <v>57662</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>128216301</v>
       </c>
       <c r="B16" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
